--- a/docs/test-cases/TC_Tahfidz_CapaianMultiSelect.xlsx
+++ b/docs/test-cases/TC_Tahfidz_CapaianMultiSelect.xlsx
@@ -2084,7 +2084,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Cypress run 6 Okt 2026 (Chrome).
+          <t>Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS. + TC-025B (BUG-006: lepas juz tanpa ayat terpilih -&gt; tanpa popup) PASS, BUG-006 FIXED.
 Pertanyaan Q5 (sheet PRD-ambigu).
 Source: judul 'Ganti Pilihan?', pesan '{Ayat} yang sudah dipilih akan dihapus ketika Anda mengganti pilihan ini. Lanjutkan?', tombol Batal/Ganti. Sesuai PRD.
 Otomasi: pilihayat.cy.js
@@ -2135,12 +2135,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>BUG-002 - Cypress run 6 Okt 2026 pasca-deploy 2a2a430e (Chrome). Evidence: docs/evidence/BUG-002/
+          <t>BUG-002 FIXED. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Otomasi: pilihayat.cy.js
 Ref manual: MSC-026 (Lepas pilihan; Scope Tiket; sumber P).</t>
         </is>
@@ -2409,12 +2409,12 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>BUG-004 - Cypress run 6 Okt 2026 pasca-deploy 2a2a430e (Chrome). Evidence: docs/evidence/BUG-004/
+          <t>BUG-004 FIXED (dimuat otomatis saat digulir). Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Pertanyaan Q3 (sheet PRD-ambigu).
 TERKONFIRMASI HTML (element analysis #2): 60 ayat per kelompok surat (badge tetap total, mis. '76 ayat'); digulir sampai dasar TIDAK menambah ayat; lanjutan hanya lewat tombol showMoreUnits('&lt;surahId&gt;') 'Muat ayat berikutnya'. Spec meng-assert bunyi PRD (digulir) -&gt; merah sampai Q3 diputuskan.
 Otomasi: pilihayat.cy.js
@@ -5099,15 +5099,14 @@
           <t>PRD</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>Manual</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Uji manual 6 Okt 2026 (dua tab admin, staging 88e43584): PASS. Simpan di tab B ditolak dan ayat yang sudah dicatat tab A tampil terkunci. Teks toast tidak direkam (deploy 88e43584 mengubah teks pesan konflik; teks baru belum dicatat). Riwayat uji QA-manual-079-B (Program #247) sudah dihapus (cleanup Cypress 6 Okt 2026: 1 passing).
-Source: pesan 'Sebagian ayat yang Anda pilih sudah dicatat pada riwayat lain. Daftar ayat dimuat ulang, silakan periksa kembali.' Sesuai PRD.
+          <t>Source: pesan 'Sebagian ayat yang Anda pilih sudah dicatat pada riwayat lain. Daftar ayat dimuat ulang, silakan periksa kembali.' Sesuai PRD.
 Manual: Butuh dua sesi admin bersamaan (tab A &amp; B). Cypress hanya menjalankan satu tab; uji manual.
 Ref manual: MSC-079 (Simpan; Scope Tiket; sumber P/D).</t>
         </is>
@@ -5213,12 +5212,12 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>BUG-005 - Cypress run 6 Okt 2026 pasca-deploy 2a2a430e (Chrome). V2 '{surat} Ayat {n}' vs PRD 'QS. {surat} ayat {n}'. Evidence: docs/evidence/BUG-005/
+          <t>BUG-005 FIXED (format 'QS. {surat} ayat {ayat}'). Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Pertanyaan Q2 (sheet PRD-ambigu).
 Source: kolom Capaian Hafalan = achievement_display_short -&gt; 'Taha Ayat 1-10' (TANPA 'QS.', 'Ayat' kapital). PRD: 'QS. Thaha ayat 1-10'. Lihat Q2.
 Otomasi: penulisancapaian.cy.js
@@ -5270,12 +5269,12 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>BUG-005 - Cypress run 6 Okt 2026 pasca-deploy 2a2a430e (Chrome). V2 '{surat} Ayat {n}' vs PRD 'QS. {surat} ayat {n}'. Evidence: docs/evidence/BUG-005/
+          <t>BUG-005 FIXED (format 'QS. {surat} ayat {ayat}'). Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Pertanyaan Q2 (sheet PRD-ambigu).
 Otomasi: penulisancapaian.cy.js
 Dijalankan di PRG-SA (Jenis Surah) karena multi surat di Jenis Juz terblokir BUG-001.
@@ -5326,12 +5325,12 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>BUG-005 - Cypress run 6 Okt 2026 pasca-deploy 2a2a430e (Chrome). V2 '{surat} Ayat {n}' vs PRD 'QS. {surat} ayat {n}'. Evidence: docs/evidence/BUG-005/
+          <t>BUG-005 FIXED (format 'QS. {surat} ayat {ayat}'). Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Pertanyaan Q2 (sheet PRD-ambigu).
 Otomasi: penulisancapaian.cy.js
 Dijalankan di PRG-SA (Jenis Surah) karena multi surat di Jenis Juz terblokir BUG-001.
@@ -5382,12 +5381,12 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>BUG-005 - Cypress run 6 Okt 2026 pasca-deploy 2a2a430e (Chrome). V2 '{surat} Ayat {n}' vs PRD 'QS. {surat} ayat {n}'. Evidence: docs/evidence/BUG-005/
+          <t>BUG-005 FIXED (format 'QS. {surat} ayat {ayat}'). Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Pertanyaan Q2 (sheet PRD-ambigu).
 Otomasi: penulisancapaian.cy.js
 Dijalankan di PRG-SA (Jenis Surah) karena multi surat di Jenis Juz terblokir BUG-001.
@@ -5438,12 +5437,12 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>BUG-005 - Cypress run 6 Okt 2026 pasca-deploy 2a2a430e (Chrome). V2 '{surat} Ayat {n}' vs PRD 'QS. {surat} ayat {n}'. Evidence: docs/evidence/BUG-005/
+          <t>BUG-005 FIXED (format 'QS. {surat} ayat {ayat}'). Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Pertanyaan Q2 (sheet PRD-ambigu).
 Source: formatUnitsShort max=2 lalu ' +{n} surat'. Sesuai PRD (kecuali prefix QS., lihat Q2).
 Otomasi: penulisancapaian.cy.js
@@ -5495,12 +5494,12 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>BUG-005 - Cypress run 6 Okt 2026 pasca-deploy 2a2a430e (Chrome). V2 '{surat} Ayat {n}' vs PRD 'QS. {surat} ayat {n}'. Evidence: docs/evidence/BUG-005/
+          <t>BUG-005 FIXED (format 'QS. {surat} ayat {ayat}'). Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Pertanyaan Q2 (sheet PRD-ambigu).
 Otomasi: penulisancapaian.cy.js
 Dijalankan di PRG-SA (Jenis Surah) karena multi surat di Jenis Juz terblokir BUG-001.
@@ -5722,12 +5721,12 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>BUG-005 - Cypress run 6 Okt 2026 pasca-deploy 2a2a430e (Chrome). V2 '{surat} Ayat {n}' vs PRD 'QS. {surat} ayat {n}'. Evidence: docs/evidence/BUG-005/
+          <t>BUG-005 FIXED (format 'QS. {surat} ayat {ayat}'). Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source export memakai achievement_display (lengkap, tanpa '+n surat'). Sesuai PRD.
 Otomasi: export.cy.js
 Dijalankan di PRG-SA (Jenis Surah) karena multi surat di Jenis Juz terblokir BUG-001.
@@ -5779,12 +5778,12 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>BUG-005 - Cypress run 6 Okt 2026 pasca-deploy 2a2a430e (Chrome). V2 '{surat} Ayat {n}' vs PRD 'QS. {surat} ayat {n}'. Evidence: docs/evidence/BUG-005/
+          <t>BUG-005 FIXED (format 'QS. {surat} ayat {ayat}'). Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Pertanyaan Q2 (sheet PRD-ambigu).
 Otomasi: export.cy.js
 Dijalankan di PRG-SA (Jenis Surah) karena multi surat di Jenis Juz terblokir BUG-001.
